--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_06/design_variables_statistics.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_06/design_variables_statistics.xlsx
@@ -495,31 +495,31 @@
         <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>70.34</v>
+        <v>71.89</v>
       </c>
       <c r="D2" t="n">
-        <v>16.34</v>
+        <v>15.12</v>
       </c>
       <c r="E2" t="n">
-        <v>23.23</v>
+        <v>21.04</v>
       </c>
       <c r="F2" t="n">
-        <v>50.06</v>
+        <v>52.37</v>
       </c>
       <c r="G2" t="n">
-        <v>55.89</v>
+        <v>60.02</v>
       </c>
       <c r="H2" t="n">
-        <v>66.41</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>84.54000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>49.94</v>
+        <v>47.63</v>
       </c>
     </row>
     <row r="3">
@@ -532,31 +532,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>43.73</v>
+        <v>41.32</v>
       </c>
       <c r="D3" t="n">
-        <v>4.71</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>10.77</v>
+        <v>20.7</v>
       </c>
       <c r="F3" t="n">
-        <v>29.82</v>
+        <v>23.13</v>
       </c>
       <c r="G3" t="n">
-        <v>42.17</v>
+        <v>45.63</v>
       </c>
       <c r="H3" t="n">
-        <v>45.96</v>
+        <v>45.78</v>
       </c>
       <c r="I3" t="n">
-        <v>46.08</v>
+        <v>46.22</v>
       </c>
       <c r="J3" t="n">
-        <v>47.32</v>
+        <v>46.85</v>
       </c>
       <c r="K3" t="n">
-        <v>17.5</v>
+        <v>23.72</v>
       </c>
     </row>
     <row r="4">
@@ -569,31 +569,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>7.87</v>
+        <v>8.49</v>
       </c>
       <c r="D4" t="n">
-        <v>2.99</v>
+        <v>3.03</v>
       </c>
       <c r="E4" t="n">
-        <v>38.02</v>
+        <v>35.7</v>
       </c>
       <c r="F4" t="n">
         <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>6.21</v>
       </c>
       <c r="H4" t="n">
-        <v>7.07</v>
+        <v>7.62</v>
       </c>
       <c r="I4" t="n">
-        <v>10.58</v>
+        <v>11.55</v>
       </c>
       <c r="J4" t="n">
-        <v>13.44</v>
+        <v>13.84</v>
       </c>
       <c r="K4" t="n">
-        <v>8.44</v>
+        <v>8.84</v>
       </c>
     </row>
     <row r="5">
@@ -606,31 +606,31 @@
         <v>50</v>
       </c>
       <c r="C5" t="n">
-        <v>89.02</v>
+        <v>83.62</v>
       </c>
       <c r="D5" t="n">
-        <v>46.14</v>
+        <v>65.27</v>
       </c>
       <c r="E5" t="n">
-        <v>51.83</v>
+        <v>78.06</v>
       </c>
       <c r="F5" t="n">
-        <v>53.07</v>
+        <v>30.19</v>
       </c>
       <c r="G5" t="n">
-        <v>57.45</v>
+        <v>37.26</v>
       </c>
       <c r="H5" t="n">
-        <v>61.71</v>
+        <v>49.16</v>
       </c>
       <c r="I5" t="n">
-        <v>130.1</v>
+        <v>174.85</v>
       </c>
       <c r="J5" t="n">
-        <v>178.18</v>
+        <v>196.56</v>
       </c>
       <c r="K5" t="n">
-        <v>125.11</v>
+        <v>166.37</v>
       </c>
     </row>
     <row r="6">
@@ -643,31 +643,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="D6" t="n">
-        <v>0.16</v>
+        <v>0.28</v>
       </c>
       <c r="E6" t="n">
-        <v>6.46</v>
+        <v>11.18</v>
       </c>
       <c r="F6" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>2.42</v>
+        <v>2.33</v>
       </c>
       <c r="H6" t="n">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="I6" t="n">
-        <v>2.58</v>
+        <v>2.76</v>
       </c>
       <c r="J6" t="n">
-        <v>3.14</v>
+        <v>3.21</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>
